--- a/public/assets/comics.xlsx
+++ b/public/assets/comics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Profesor MCSD Mañana\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alumnos MCSD Mañana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E44510E-6EC8-41AC-9079-26B0A7D6E8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3258CC85-28DA-4B15-A9CD-D0E8621C5C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="45.85546875" customWidth="1"/>
+    <col min="2" max="2" width="101.42578125" customWidth="1"/>
     <col min="3" max="3" width="44.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -510,6 +510,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d864b491-0338-416e-8b5c-676b35e3c799">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3a60703c-8de3-4d2f-986e-a71118bb65bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DDE02CC757EA05468583ADD4AF129010" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5f10fc941063c0463228b1370efbca61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d864b491-0338-416e-8b5c-676b35e3c799" xmlns:ns3="3a60703c-8de3-4d2f-986e-a71118bb65bf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6fe1f0ebf7a652d23249c2c4f816993" ns2:_="" ns3:_="">
     <xsd:import namespace="d864b491-0338-416e-8b5c-676b35e3c799"/>
@@ -702,34 +722,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d864b491-0338-416e-8b5c-676b35e3c799">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3a60703c-8de3-4d2f-986e-a71118bb65bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB2720E0-D9D5-4BB9-BBF7-3A35D98E3C94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89F9A26-2AA2-4A24-B2FE-F854ACCA57D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d864b491-0338-416e-8b5c-676b35e3c799"/>
+    <ds:schemaRef ds:uri="3a60703c-8de3-4d2f-986e-a71118bb65bf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F15FC3DC-B8BA-48CD-A436-54037E58127B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F15FC3DC-B8BA-48CD-A436-54037E58127B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89F9A26-2AA2-4A24-B2FE-F854ACCA57D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB2720E0-D9D5-4BB9-BBF7-3A35D98E3C94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d864b491-0338-416e-8b5c-676b35e3c799"/>
+    <ds:schemaRef ds:uri="3a60703c-8de3-4d2f-986e-a71118bb65bf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>